--- a/artfynd/A 40123-2021 artfynd.xlsx
+++ b/artfynd/A 40123-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40123-2021 artfynd.xlsx
+++ b/artfynd/A 40123-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>6771503</v>
       </c>
       <c r="B2" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585087.3196389347</v>
+        <v>585087</v>
       </c>
       <c r="R2" t="n">
-        <v>6909666.166581781</v>
+        <v>6909666</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2004-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,6 +774,344 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1981139</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Snårkullen (17G2i10), Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>585087</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6909666</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2004-08-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2004-08-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>170628101 / LOB PULM / Enstaka-sparsam (1)  / OBJ.AREA:0,6 ha</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Rasbrant /</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gammal sälg</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3015831</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Snårkullen (17G2i10), Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>585087</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6909666</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2004-08-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2004-08-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>170628101 / GOOD REP / Enstaka-sparsam (1)  / OBJ.AREA:0,6 ha</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Rasbrant /</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4353148</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Snårkullen (17G2i10), Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>585087</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6909666</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2004-08-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2004-08-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>170628101 / LIST COR / Enstaka-sparsam (1)  / OBJ.AREA:0,6 ha</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Rasbrant /</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Michold</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>

--- a/artfynd/A 40123-2021 artfynd.xlsx
+++ b/artfynd/A 40123-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6771503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1981139</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3015831</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4353148</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>